--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009672143248027117</v>
+        <v>0.009720922013096014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009672143248027117</v>
+        <v>0.009720922013096014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004347451335618737</v>
+        <v>0.004998847793112752</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009209123441506734</v>
+        <v>0.009158407542438612</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009209123441506734</v>
+        <v>0.009158407542438612</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003859148234742732</v>
+        <v>0.004353433946720067</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.008789226169675129</v>
+        <v>0.008666422447883817</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008789226169675129</v>
+        <v>0.008666422447883817</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003291410084526618</v>
+        <v>0.003756631511254301</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008725301044809985</v>
+        <v>0.008593786295690615</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008725301044809985</v>
+        <v>0.008593786295690615</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002643814040251027</v>
+        <v>0.002975569582595628</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009321485263748597</v>
+        <v>0.009237757915958707</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009321485263748597</v>
+        <v>0.009237757915958707</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002238445276528535</v>
+        <v>0.00240990920166058</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0107657944633706</v>
+        <v>0.0107716622540735</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0107657944633706</v>
+        <v>0.0107716622540735</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00223954194611208</v>
+        <v>0.002409357752874702</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0133538229953937</v>
+        <v>0.01347944020191495</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0133538229953937</v>
+        <v>0.01347944020191495</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002481653756888819</v>
+        <v>0.002541373580048092</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01693685496268735</v>
+        <v>0.01719066309269265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01693685496268735</v>
+        <v>0.01719066309269265</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0031406289673659</v>
+        <v>0.002797432770837791</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02123359501483464</v>
+        <v>0.02158944617041213</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02123359501483464</v>
+        <v>0.02158944617041213</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004798673529141589</v>
+        <v>0.004377608849376195</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02586587119719335</v>
+        <v>0.0262649447630087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02586587119719335</v>
+        <v>0.0262649447630087</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006500011947226232</v>
+        <v>0.006316215570226529</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03030136450420191</v>
+        <v>0.03068154811301191</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03030136450420191</v>
+        <v>0.03068154811301191</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006566629598677857</v>
+        <v>0.00637028570920092</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03504949800078807</v>
+        <v>0.03540726441782321</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03504949800078807</v>
+        <v>0.03540726441782321</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005277342782459686</v>
+        <v>0.004722828285644512</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.04074426072110067</v>
+        <v>0.04114233193211966</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04074426072110067</v>
+        <v>0.04114233193211966</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004370523026601264</v>
+        <v>0.003295348300255815</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04710393584796548</v>
+        <v>0.04761473508404696</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04710393584796548</v>
+        <v>0.04761473508404696</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004607068585395271</v>
+        <v>0.003383260910534068</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05326749434876947</v>
+        <v>0.05392229822778119</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05326749434876947</v>
+        <v>0.05392229822778119</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005324794482965326</v>
+        <v>0.004046425811047884</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0583010961274231</v>
+        <v>0.05908858836655403</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0583010961274231</v>
+        <v>0.05908858836655403</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006122332992048843</v>
+        <v>0.004610933510726853</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06259573260758645</v>
+        <v>0.0634824930089153</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06259573260758645</v>
+        <v>0.0634824930089153</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006995857236845175</v>
+        <v>0.005142057619823195</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06558300360666316</v>
+        <v>0.06652510280854916</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06558300360666316</v>
+        <v>0.06652510280854916</v>
       </c>
       <c r="D19" t="n">
-        <v>0.007903659411284415</v>
+        <v>0.005692632126263896</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06749437506397118</v>
+        <v>0.06844143461944162</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06749437506397118</v>
+        <v>0.06844143461944162</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008771737602604095</v>
+        <v>0.006274217848728511</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06818827813356899</v>
+        <v>0.06909796487527153</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06818827813356899</v>
+        <v>0.06909796487527153</v>
       </c>
       <c r="D21" t="n">
-        <v>0.009469571284677623</v>
+        <v>0.006771110130085512</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06843721366128912</v>
+        <v>0.06929165903101597</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06843721366128912</v>
+        <v>0.06929165903101597</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01008089112800862</v>
+        <v>0.007184914799500917</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06741376836339383</v>
+        <v>0.06820511299154561</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06741376836339383</v>
+        <v>0.06820511299154561</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01042947131055461</v>
+        <v>0.007380378890077872</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0662265238344478</v>
+        <v>0.06696840946007625</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0662265238344478</v>
+        <v>0.06696840946007625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01060857187427502</v>
+        <v>0.00746785510869298</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06466192300225612</v>
+        <v>0.06538125561577522</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06466192300225612</v>
+        <v>0.06538125561577522</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01060142029895386</v>
+        <v>0.007500304891567214</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06285909605002224</v>
+        <v>0.063572959644663</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06285909605002224</v>
+        <v>0.063572959644663</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01051665649850088</v>
+        <v>0.007575473232768672</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0612261440841546</v>
+        <v>0.0619213987547395</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0612261440841546</v>
+        <v>0.0619213987547395</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01044964126171959</v>
+        <v>0.007625940833440079</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.05863917741181254</v>
+        <v>0.05933615918083151</v>
       </c>
       <c r="C28" t="n">
-        <v>0.05863917741181254</v>
+        <v>0.05933615918083151</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01033507759006474</v>
+        <v>0.007813522017450449</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.05696617813615144</v>
+        <v>0.05765545004566154</v>
       </c>
       <c r="C29" t="n">
-        <v>0.05696617813615144</v>
+        <v>0.05765545004566154</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01034541033682713</v>
+        <v>0.007927753350208747</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05610339552954388</v>
+        <v>0.05681294238305959</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05610339552954388</v>
+        <v>0.05681294238305959</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01034175825128283</v>
+        <v>0.008142542275891181</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05494555472480018</v>
+        <v>0.05565326064786354</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05494555472480018</v>
+        <v>0.05565326064786354</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01043538183675368</v>
+        <v>0.008256234339251533</v>
       </c>
     </row>
   </sheetData>
